--- a/XBRL-template-MFRS/Group/04-SOPL-Nature.xlsx
+++ b/XBRL-template-MFRS/Group/04-SOPL-Nature.xlsx
@@ -629,10 +629,22 @@
           <t>Other income</t>
         </is>
       </c>
-      <c r="B8" s="22" t="n"/>
-      <c r="C8" s="22" t="n"/>
-      <c r="D8" s="22" t="n"/>
-      <c r="E8" s="22" t="n"/>
+      <c r="B8" s="22">
+        <f>'SOPL-Analysis-Nature'!B83</f>
+        <v/>
+      </c>
+      <c r="C8" s="22">
+        <f>'SOPL-Analysis-Nature'!C83</f>
+        <v/>
+      </c>
+      <c r="D8" s="22">
+        <f>'SOPL-Analysis-Nature'!D83</f>
+        <v/>
+      </c>
+      <c r="E8" s="22">
+        <f>'SOPL-Analysis-Nature'!E83</f>
+        <v/>
+      </c>
     </row>
     <row r="9" ht="18" customHeight="1" s="12">
       <c r="A9" s="21" t="inlineStr">
@@ -707,10 +719,22 @@
           <t>Other expenses, by nature</t>
         </is>
       </c>
-      <c r="B14" s="22" t="n"/>
-      <c r="C14" s="22" t="n"/>
-      <c r="D14" s="22" t="n"/>
-      <c r="E14" s="22" t="n"/>
+      <c r="B14" s="22">
+        <f>'SOPL-Analysis-Nature'!B128</f>
+        <v/>
+      </c>
+      <c r="C14" s="22">
+        <f>'SOPL-Analysis-Nature'!C128</f>
+        <v/>
+      </c>
+      <c r="D14" s="22">
+        <f>'SOPL-Analysis-Nature'!D128</f>
+        <v/>
+      </c>
+      <c r="E14" s="22">
+        <f>'SOPL-Analysis-Nature'!E128</f>
+        <v/>
+      </c>
     </row>
     <row r="15" ht="18" customHeight="1" s="12">
       <c r="A15" s="19" t="inlineStr">
@@ -719,19 +743,19 @@
         </is>
       </c>
       <c r="B15" s="20">
-        <f>1*B7+1*B8+1*B9+1*B10+-1*B11+-1*B12+-1*B13+-1*B14</f>
+        <f>1*B7+1*B8+-1*B9+1*B10+-1*B11+-1*B12+-1*B13+-1*B14</f>
         <v/>
       </c>
       <c r="C15" s="20">
-        <f>1*C7+1*C8+1*C9+1*C10+-1*C11+-1*C12+-1*C13+-1*C14</f>
+        <f>1*C7+1*C8+-1*C9+1*C10+-1*C11+-1*C12+-1*C13+-1*C14</f>
         <v/>
       </c>
       <c r="D15" s="20">
-        <f>1*D7+1*D8+1*D9+1*D10+-1*D11+-1*D12+-1*D13+-1*D14</f>
+        <f>1*D7+1*D8+-1*D9+1*D10+-1*D11+-1*D12+-1*D13+-1*D14</f>
         <v/>
       </c>
       <c r="E15" s="20">
-        <f>1*E7+1*E8+1*E9+1*E10+-1*E11+-1*E12+-1*E13+-1*E14</f>
+        <f>1*E7+1*E8+-1*E9+1*E10+-1*E11+-1*E12+-1*E13+-1*E14</f>
         <v/>
       </c>
     </row>
@@ -741,10 +765,22 @@
           <t>Finance income</t>
         </is>
       </c>
-      <c r="B16" s="22" t="n"/>
-      <c r="C16" s="22" t="n"/>
-      <c r="D16" s="22" t="n"/>
-      <c r="E16" s="22" t="n"/>
+      <c r="B16" s="22">
+        <f>'SOPL-Analysis-Nature'!B132</f>
+        <v/>
+      </c>
+      <c r="C16" s="22">
+        <f>'SOPL-Analysis-Nature'!C132</f>
+        <v/>
+      </c>
+      <c r="D16" s="22">
+        <f>'SOPL-Analysis-Nature'!D132</f>
+        <v/>
+      </c>
+      <c r="E16" s="22">
+        <f>'SOPL-Analysis-Nature'!E132</f>
+        <v/>
+      </c>
     </row>
     <row r="17" ht="18" customHeight="1" s="12">
       <c r="A17" s="21" t="inlineStr">
@@ -775,19 +811,19 @@
         </is>
       </c>
       <c r="B19" s="20">
-        <f>1*B15+1*B16+-1*B17+1*B18</f>
+        <f>1*B7+1*B8+-1*B9+1*B10+-1*B11+-1*B12+-1*B13+-1*B14+1*B16+-1*B17+1*B18</f>
         <v/>
       </c>
       <c r="C19" s="20">
-        <f>1*C15+1*C16+-1*C17+1*C18</f>
+        <f>1*C7+1*C8+-1*C9+1*C10+-1*C11+-1*C12+-1*C13+-1*C14+1*C16+-1*C17+1*C18</f>
         <v/>
       </c>
       <c r="D19" s="20">
-        <f>1*D15+1*D16+-1*D17+1*D18</f>
+        <f>1*D7+1*D8+-1*D9+1*D10+-1*D11+-1*D12+-1*D13+-1*D14+1*D16+-1*D17+1*D18</f>
         <v/>
       </c>
       <c r="E19" s="20">
-        <f>1*E15+1*E16+-1*E17+1*E18</f>
+        <f>1*E7+1*E8+-1*E9+1*E10+-1*E11+-1*E12+-1*E13+-1*E14+1*E16+-1*E17+1*E18</f>
         <v/>
       </c>
     </row>
@@ -1285,10 +1321,22 @@
           <t>Revenue from sale of goods</t>
         </is>
       </c>
-      <c r="B16" s="24" t="n"/>
-      <c r="C16" s="24" t="n"/>
-      <c r="D16" s="24" t="n"/>
-      <c r="E16" s="24" t="n"/>
+      <c r="B16" s="24">
+        <f>1*B8+1*B9+1*B10+1*B11+1*B12+1*B13+1*B14+1*B15</f>
+        <v/>
+      </c>
+      <c r="C16" s="24">
+        <f>1*C8+1*C9+1*C10+1*C11+1*C12+1*C13+1*C14+1*C15</f>
+        <v/>
+      </c>
+      <c r="D16" s="24">
+        <f>1*D8+1*D9+1*D10+1*D11+1*D12+1*D13+1*D14+1*D15</f>
+        <v/>
+      </c>
+      <c r="E16" s="24">
+        <f>1*E8+1*E9+1*E10+1*E11+1*E12+1*E13+1*E14+1*E15</f>
+        <v/>
+      </c>
     </row>
     <row r="17" ht="18" customHeight="1" s="12">
       <c r="A17" s="17" t="inlineStr">
@@ -1318,22 +1366,10 @@
           <t>Total revenue from rendering of telecommunication services</t>
         </is>
       </c>
-      <c r="B19" s="20">
-        <f>1*B8+1*B9+1*B10+1*B11+1*B12+1*B13+1*B14+1*B15+1*B16+1*B18</f>
-        <v/>
-      </c>
-      <c r="C19" s="20">
-        <f>1*C8+1*C9+1*C10+1*C11+1*C12+1*C13+1*C14+1*C15+1*C16+1*C18</f>
-        <v/>
-      </c>
-      <c r="D19" s="20">
-        <f>1*D8+1*D9+1*D10+1*D11+1*D12+1*D13+1*D14+1*D15+1*D16+1*D18</f>
-        <v/>
-      </c>
-      <c r="E19" s="20">
-        <f>1*E8+1*E9+1*E10+1*E11+1*E12+1*E13+1*E14+1*E15+1*E16+1*E18</f>
-        <v/>
-      </c>
+      <c r="B19" s="20" t="n"/>
+      <c r="C19" s="20" t="n"/>
+      <c r="D19" s="20" t="n"/>
+      <c r="E19" s="20" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1" s="12">
       <c r="A20" s="21" t="inlineStr">
@@ -1407,10 +1443,22 @@
           <t>Revenue from rendering of services</t>
         </is>
       </c>
-      <c r="B26" s="24" t="n"/>
-      <c r="C26" s="24" t="n"/>
-      <c r="D26" s="24" t="n"/>
-      <c r="E26" s="24" t="n"/>
+      <c r="B26" s="24">
+        <f>1*B18+1*B19+1*B20+1*B21+1*B22+1*B23+1*B24+1*B25</f>
+        <v/>
+      </c>
+      <c r="C26" s="24">
+        <f>1*C18+1*C19+1*C20+1*C21+1*C22+1*C23+1*C24+1*C25</f>
+        <v/>
+      </c>
+      <c r="D26" s="24">
+        <f>1*D18+1*D19+1*D20+1*D21+1*D22+1*D23+1*D24+1*D25</f>
+        <v/>
+      </c>
+      <c r="E26" s="24">
+        <f>1*E18+1*E19+1*E20+1*E21+1*E22+1*E23+1*E24+1*E25</f>
+        <v/>
+      </c>
     </row>
     <row r="27" ht="18" customHeight="1" s="12">
       <c r="A27" s="17" t="inlineStr">
@@ -1451,10 +1499,22 @@
           <t>Interest income</t>
         </is>
       </c>
-      <c r="B30" s="24" t="n"/>
-      <c r="C30" s="24" t="n"/>
-      <c r="D30" s="24" t="n"/>
-      <c r="E30" s="24" t="n"/>
+      <c r="B30" s="24">
+        <f>1*B28+1*B29</f>
+        <v/>
+      </c>
+      <c r="C30" s="24">
+        <f>1*C28+1*C29</f>
+        <v/>
+      </c>
+      <c r="D30" s="24">
+        <f>1*D28+1*D29</f>
+        <v/>
+      </c>
+      <c r="E30" s="24">
+        <f>1*E28+1*E29</f>
+        <v/>
+      </c>
     </row>
     <row r="31" ht="18" customHeight="1" s="12">
       <c r="A31" s="17" t="inlineStr">
@@ -1507,19 +1567,19 @@
         </is>
       </c>
       <c r="B35" s="20">
-        <f>1*B20+1*B21+1*B22+1*B23+1*B24+1*B25+1*B26+1*B28+1*B29+1*B30+1*B32+1*B33+1*B34</f>
+        <f>1*B32+1*B33+1*B34</f>
         <v/>
       </c>
       <c r="C35" s="20">
-        <f>1*C20+1*C21+1*C22+1*C23+1*C24+1*C25+1*C26+1*C28+1*C29+1*C30+1*C32+1*C33+1*C34</f>
+        <f>1*C32+1*C33+1*C34</f>
         <v/>
       </c>
       <c r="D35" s="20">
-        <f>1*D20+1*D21+1*D22+1*D23+1*D24+1*D25+1*D26+1*D28+1*D29+1*D30+1*D32+1*D33+1*D34</f>
+        <f>1*D32+1*D33+1*D34</f>
         <v/>
       </c>
       <c r="E35" s="20">
-        <f>1*E20+1*E21+1*E22+1*E23+1*E24+1*E25+1*E26+1*E28+1*E29+1*E30+1*E32+1*E33+1*E34</f>
+        <f>1*E32+1*E33+1*E34</f>
         <v/>
       </c>
     </row>
@@ -1574,19 +1634,19 @@
         </is>
       </c>
       <c r="B40" s="23">
-        <f>1*B36+1*B37+1*B38+1*B39</f>
+        <f>1*B16+1*B26+1*B30+1*B35+1*B36+1*B37+1*B38+1*B39</f>
         <v/>
       </c>
       <c r="C40" s="23">
-        <f>1*C36+1*C37+1*C38+1*C39</f>
+        <f>1*C16+1*C26+1*C30+1*C35+1*C36+1*C37+1*C38+1*C39</f>
         <v/>
       </c>
       <c r="D40" s="23">
-        <f>1*D36+1*D37+1*D38+1*D39</f>
+        <f>1*D16+1*D26+1*D30+1*D35+1*D36+1*D37+1*D38+1*D39</f>
         <v/>
       </c>
       <c r="E40" s="23">
-        <f>1*E36+1*E37+1*E38+1*E39</f>
+        <f>1*E16+1*E26+1*E30+1*E35+1*E36+1*E37+1*E38+1*E39</f>
         <v/>
       </c>
     </row>
@@ -1761,10 +1821,22 @@
           <t>Gains on foreign exchange</t>
         </is>
       </c>
-      <c r="B56" s="24" t="n"/>
-      <c r="C56" s="24" t="n"/>
-      <c r="D56" s="24" t="n"/>
-      <c r="E56" s="24" t="n"/>
+      <c r="B56" s="24">
+        <f>1*B54+1*B55</f>
+        <v/>
+      </c>
+      <c r="C56" s="24">
+        <f>1*C54+1*C55</f>
+        <v/>
+      </c>
+      <c r="D56" s="24">
+        <f>1*D54+1*D55</f>
+        <v/>
+      </c>
+      <c r="E56" s="24">
+        <f>1*E54+1*E55</f>
+        <v/>
+      </c>
     </row>
     <row r="57" ht="18" customHeight="1" s="12">
       <c r="A57" s="17" t="inlineStr">
@@ -1816,10 +1888,22 @@
           <t>Gain from disposal of a subsidiary, joint ventures and associates</t>
         </is>
       </c>
-      <c r="B61" s="22" t="n"/>
-      <c r="C61" s="22" t="n"/>
-      <c r="D61" s="22" t="n"/>
-      <c r="E61" s="22" t="n"/>
+      <c r="B61" s="22">
+        <f>1*B58+1*B59+1*B60</f>
+        <v/>
+      </c>
+      <c r="C61" s="22">
+        <f>1*C58+1*C59+1*C60</f>
+        <v/>
+      </c>
+      <c r="D61" s="22">
+        <f>1*D58+1*D59+1*D60</f>
+        <v/>
+      </c>
+      <c r="E61" s="22">
+        <f>1*E58+1*E59+1*E60</f>
+        <v/>
+      </c>
     </row>
     <row r="62" ht="18" customHeight="1" s="12">
       <c r="A62" s="21" t="inlineStr">
@@ -1937,10 +2021,22 @@
           <t>Reversal of impairment loss recognised in profit or loss</t>
         </is>
       </c>
-      <c r="B72" s="22" t="n"/>
-      <c r="C72" s="22" t="n"/>
-      <c r="D72" s="22" t="n"/>
-      <c r="E72" s="22" t="n"/>
+      <c r="B72" s="22">
+        <f>1*B67+1*B68+1*B69+1*B70+1*B71</f>
+        <v/>
+      </c>
+      <c r="C72" s="22">
+        <f>1*C67+1*C68+1*C69+1*C70+1*C71</f>
+        <v/>
+      </c>
+      <c r="D72" s="22">
+        <f>1*D67+1*D68+1*D69+1*D70+1*D71</f>
+        <v/>
+      </c>
+      <c r="E72" s="22">
+        <f>1*E67+1*E68+1*E69+1*E70+1*E71</f>
+        <v/>
+      </c>
     </row>
     <row r="73" ht="18" customHeight="1" s="12">
       <c r="A73" s="21" t="inlineStr">
@@ -2058,10 +2154,22 @@
           <t>Other income</t>
         </is>
       </c>
-      <c r="B83" s="24" t="n"/>
-      <c r="C83" s="24" t="n"/>
-      <c r="D83" s="24" t="n"/>
-      <c r="E83" s="24" t="n"/>
+      <c r="B83" s="24">
+        <f>1*B42+1*B43+1*B44+1*B45+1*B46+1*B47+1*B48+1*B49+1*B50+1*B51+1*B52+1*B56+1*B61+1*B62+1*B63+1*B64+1*B65+1*B72+1*B73+1*B74+1*B75+1*B76+1*B77+1*B78+1*B79+1*B80+1*B81+1*B82</f>
+        <v/>
+      </c>
+      <c r="C83" s="24">
+        <f>1*C42+1*C43+1*C44+1*C45+1*C46+1*C47+1*C48+1*C49+1*C50+1*C51+1*C52+1*C56+1*C61+1*C62+1*C63+1*C64+1*C65+1*C72+1*C73+1*C74+1*C75+1*C76+1*C77+1*C78+1*C79+1*C80+1*C81+1*C82</f>
+        <v/>
+      </c>
+      <c r="D83" s="24">
+        <f>1*D42+1*D43+1*D44+1*D45+1*D46+1*D47+1*D48+1*D49+1*D50+1*D51+1*D52+1*D56+1*D61+1*D62+1*D63+1*D64+1*D65+1*D72+1*D73+1*D74+1*D75+1*D76+1*D77+1*D78+1*D79+1*D80+1*D81+1*D82</f>
+        <v/>
+      </c>
+      <c r="E83" s="24">
+        <f>1*E42+1*E43+1*E44+1*E45+1*E46+1*E47+1*E48+1*E49+1*E50+1*E51+1*E52+1*E56+1*E61+1*E62+1*E63+1*E64+1*E65+1*E72+1*E73+1*E74+1*E75+1*E76+1*E77+1*E78+1*E79+1*E80+1*E81+1*E82</f>
+        <v/>
+      </c>
     </row>
     <row r="84" ht="18" customHeight="1" s="12">
       <c r="A84" s="17" t="inlineStr">
@@ -2135,22 +2243,10 @@
           <t>Total post-employment benefit expense in profit or loss, defined benefit plans</t>
         </is>
       </c>
-      <c r="B90" s="20">
-        <f>1*B42+1*B43+1*B44+1*B45+1*B46+1*B47+1*B48+1*B49+1*B50+1*B51+1*B52+1*B54+1*B55+1*B56+1*B58+1*B59+1*B60+1*B61+1*B62+1*B63+1*B64+1*B65+1*B67+1*B68+1*B69+1*B70+1*B71+1*B72+1*B73+1*B74+1*B75+1*B76+1*B77+1*B78+1*B79+1*B80+1*B81+1*B82+1*B83+1*B85+1*B86+1*B87+1*B88+1*B89</f>
-        <v/>
-      </c>
-      <c r="C90" s="20">
-        <f>1*C42+1*C43+1*C44+1*C45+1*C46+1*C47+1*C48+1*C49+1*C50+1*C51+1*C52+1*C54+1*C55+1*C56+1*C58+1*C59+1*C60+1*C61+1*C62+1*C63+1*C64+1*C65+1*C67+1*C68+1*C69+1*C70+1*C71+1*C72+1*C73+1*C74+1*C75+1*C76+1*C77+1*C78+1*C79+1*C80+1*C81+1*C82+1*C83+1*C85+1*C86+1*C87+1*C88+1*C89</f>
-        <v/>
-      </c>
-      <c r="D90" s="20">
-        <f>1*D42+1*D43+1*D44+1*D45+1*D46+1*D47+1*D48+1*D49+1*D50+1*D51+1*D52+1*D54+1*D55+1*D56+1*D58+1*D59+1*D60+1*D61+1*D62+1*D63+1*D64+1*D65+1*D67+1*D68+1*D69+1*D70+1*D71+1*D72+1*D73+1*D74+1*D75+1*D76+1*D77+1*D78+1*D79+1*D80+1*D81+1*D82+1*D83+1*D85+1*D86+1*D87+1*D88+1*D89</f>
-        <v/>
-      </c>
-      <c r="E90" s="20">
-        <f>1*E42+1*E43+1*E44+1*E45+1*E46+1*E47+1*E48+1*E49+1*E50+1*E51+1*E52+1*E54+1*E55+1*E56+1*E58+1*E59+1*E60+1*E61+1*E62+1*E63+1*E64+1*E65+1*E67+1*E68+1*E69+1*E70+1*E71+1*E72+1*E73+1*E74+1*E75+1*E76+1*E77+1*E78+1*E79+1*E80+1*E81+1*E82+1*E83+1*E85+1*E86+1*E87+1*E88+1*E89</f>
-        <v/>
-      </c>
+      <c r="B90" s="20" t="n"/>
+      <c r="C90" s="20" t="n"/>
+      <c r="D90" s="20" t="n"/>
+      <c r="E90" s="20" t="n"/>
     </row>
     <row r="91" ht="18" customHeight="1" s="12">
       <c r="A91" s="21" t="inlineStr">
@@ -2203,19 +2299,19 @@
         </is>
       </c>
       <c r="B95" s="23">
-        <f>1*B91+1*B92+1*B93+1*B94</f>
+        <f>1*B85+1*B86+1*B87+1*B88+1*B89+1*B90+1*B91+1*B92+1*B93+1*B94</f>
         <v/>
       </c>
       <c r="C95" s="23">
-        <f>1*C91+1*C92+1*C93+1*C94</f>
+        <f>1*C85+1*C86+1*C87+1*C88+1*C89+1*C90+1*C91+1*C92+1*C93+1*C94</f>
         <v/>
       </c>
       <c r="D95" s="23">
-        <f>1*D91+1*D92+1*D93+1*D94</f>
+        <f>1*D85+1*D86+1*D87+1*D88+1*D89+1*D90+1*D91+1*D92+1*D93+1*D94</f>
         <v/>
       </c>
       <c r="E95" s="23">
-        <f>1*E91+1*E92+1*E93+1*E94</f>
+        <f>1*E85+1*E86+1*E87+1*E88+1*E89+1*E90+1*E91+1*E92+1*E93+1*E94</f>
         <v/>
       </c>
     </row>
@@ -2369,10 +2465,22 @@
           <t>Loss on disposal of subsidiaries, joint ventures and associates</t>
         </is>
       </c>
-      <c r="B108" s="22" t="n"/>
-      <c r="C108" s="22" t="n"/>
-      <c r="D108" s="22" t="n"/>
-      <c r="E108" s="22" t="n"/>
+      <c r="B108" s="22">
+        <f>1*B105+1*B106+1*B107</f>
+        <v/>
+      </c>
+      <c r="C108" s="22">
+        <f>1*C105+1*C106+1*C107</f>
+        <v/>
+      </c>
+      <c r="D108" s="22">
+        <f>1*D105+1*D106+1*D107</f>
+        <v/>
+      </c>
+      <c r="E108" s="22">
+        <f>1*E105+1*E106+1*E107</f>
+        <v/>
+      </c>
     </row>
     <row r="109" ht="18" customHeight="1" s="12">
       <c r="A109" s="21" t="inlineStr">
@@ -2567,10 +2675,22 @@
           <t>Director's remuneration</t>
         </is>
       </c>
-      <c r="B126" s="22" t="n"/>
-      <c r="C126" s="22" t="n"/>
-      <c r="D126" s="22" t="n"/>
-      <c r="E126" s="22" t="n"/>
+      <c r="B126" s="22">
+        <f>1*B117+1*B118+1*B119+1*B120+1*B121+1*B122+1*B123+1*B124+1*B125</f>
+        <v/>
+      </c>
+      <c r="C126" s="22">
+        <f>1*C117+1*C118+1*C119+1*C120+1*C121+1*C122+1*C123+1*C124+1*C125</f>
+        <v/>
+      </c>
+      <c r="D126" s="22">
+        <f>1*D117+1*D118+1*D119+1*D120+1*D121+1*D122+1*D123+1*D124+1*D125</f>
+        <v/>
+      </c>
+      <c r="E126" s="22">
+        <f>1*E117+1*E118+1*E119+1*E120+1*E121+1*E122+1*E123+1*E124+1*E125</f>
+        <v/>
+      </c>
     </row>
     <row r="127" ht="18" customHeight="1" s="12">
       <c r="A127" s="21" t="inlineStr">
@@ -2589,10 +2709,22 @@
           <t>Other expenses, by nature</t>
         </is>
       </c>
-      <c r="B128" s="24" t="n"/>
-      <c r="C128" s="24" t="n"/>
-      <c r="D128" s="24" t="n"/>
-      <c r="E128" s="24" t="n"/>
+      <c r="B128" s="24">
+        <f>1*B100+1*B101+1*B102+1*B103+1*B108+1*B109+1*B110+1*B111+1*B112+1*B113+1*B114+1*B115+1*B126+1*B127</f>
+        <v/>
+      </c>
+      <c r="C128" s="24">
+        <f>1*C100+1*C101+1*C102+1*C103+1*C108+1*C109+1*C110+1*C111+1*C112+1*C113+1*C114+1*C115+1*C126+1*C127</f>
+        <v/>
+      </c>
+      <c r="D128" s="24">
+        <f>1*D100+1*D101+1*D102+1*D103+1*D108+1*D109+1*D110+1*D111+1*D112+1*D113+1*D114+1*D115+1*D126+1*D127</f>
+        <v/>
+      </c>
+      <c r="E128" s="24">
+        <f>1*E100+1*E101+1*E102+1*E103+1*E108+1*E109+1*E110+1*E111+1*E112+1*E113+1*E114+1*E115+1*E126+1*E127</f>
+        <v/>
+      </c>
     </row>
     <row r="129" ht="18" customHeight="1" s="12">
       <c r="A129" s="17" t="inlineStr">
@@ -2633,10 +2765,22 @@
           <t>Finance income</t>
         </is>
       </c>
-      <c r="B132" s="22" t="n"/>
-      <c r="C132" s="22" t="n"/>
-      <c r="D132" s="22" t="n"/>
-      <c r="E132" s="22" t="n"/>
+      <c r="B132" s="22">
+        <f>1*B130+1*B131</f>
+        <v/>
+      </c>
+      <c r="C132" s="22">
+        <f>1*C130+1*C131</f>
+        <v/>
+      </c>
+      <c r="D132" s="22">
+        <f>1*D130+1*D131</f>
+        <v/>
+      </c>
+      <c r="E132" s="22">
+        <f>1*E130+1*E131</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
